--- a/demo/5_参照つき.xlsx
+++ b/demo/5_参照つき.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="売上" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="売上表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="報告" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B1">
-        <f>売上!B2</f>
+        <f>売上表!B2</f>
         <v/>
       </c>
     </row>
